--- a/gte/nodes/HPT/turbine_blade_strength.xlsx
+++ b/gte/nodes/HPT/turbine_blade_strength.xlsx
@@ -1183,112 +1183,112 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>333.98357778847736</v>
+        <v>333.98357778847742</v>
       </c>
       <c r="C3">
-        <v>115.67176724280817</v>
+        <v>115.62689130445044</v>
       </c>
       <c r="D3">
-        <v>15.186777844152577</v>
+        <v>15.180885992384107</v>
       </c>
       <c r="E3">
-        <v>131.29200155016051</v>
+        <v>131.29200155016014</v>
       </c>
       <c r="F3">
-        <v>171.20607131219583</v>
+        <v>171.13965032386037</v>
       </c>
       <c r="G3">
-        <v>474.06987630185256</v>
+        <v>473.86551064294986</v>
       </c>
       <c r="H3">
-        <v>20.747186642416278</v>
+        <v>20.739137578318228</v>
       </c>
       <c r="I3">
-        <v>121.18254033517066</v>
+        <v>121.18254033517076</v>
       </c>
       <c r="J3">
         <v>2705.1966216148621</v>
       </c>
       <c r="K3">
-        <v>941.6483665161013</v>
+        <v>939.17006936673044</v>
       </c>
       <c r="L3">
-        <v>850.00194622173285</v>
+        <v>847.21940418293445</v>
       </c>
       <c r="M3">
         <v>5.3007432949812827</v>
       </c>
       <c r="N3">
-        <v>2.3128417767685341</v>
+        <v>2.3079576233724075</v>
       </c>
       <c r="O3">
-        <v>2.126858296867935</v>
+        <v>2.1201211138825826</v>
       </c>
       <c r="P3">
         <v>5.3007432949812827</v>
       </c>
       <c r="Q3">
-        <v>2.3128417767685341</v>
+        <v>2.3079576233724075</v>
       </c>
       <c r="R3">
-        <v>2.126858296867935</v>
+        <v>2.1201211138825826</v>
       </c>
       <c r="S3">
         <v>100</v>
       </c>
       <c r="T3">
-        <v>231.48743451711223</v>
+        <v>231.94032063432368</v>
       </c>
       <c r="U3">
-        <v>145.8840517300419</v>
+        <v>147.26949144694035</v>
       </c>
       <c r="V3">
         <v>6.1230317691118863E-15</v>
       </c>
       <c r="W3">
-        <v>896.73361542274142</v>
+        <v>897.67971008746952</v>
       </c>
       <c r="X3">
-        <v>2.7400691012432512</v>
+        <v>1.7634768590987235</v>
       </c>
       <c r="Y3">
-        <v>16.161032657442711</v>
+        <v>16.157897441835104</v>
       </c>
       <c r="Z3">
-        <v>28.629221472316949</v>
+        <v>28.623049955528398</v>
       </c>
       <c r="AA3">
-        <v>10.014348695018649</v>
+        <v>10.001208502985811</v>
       </c>
       <c r="AB3">
-        <v>8.9348379579812924</v>
+        <v>8.9312659082442742</v>
       </c>
       <c r="AC3">
-        <v>6.7560467245308145</v>
+        <v>6.75061762590563</v>
       </c>
       <c r="AD3">
-        <v>3.702975538147343</v>
+        <v>3.7023287925477355</v>
       </c>
       <c r="AE3">
-        <v>1484.5960700350806</v>
+        <v>1481.979293895906</v>
       </c>
       <c r="AF3">
-        <v>5992.0040733827327</v>
+        <v>5985.7978485632621</v>
       </c>
       <c r="AG3">
-        <v>14051.675294569524</v>
+        <v>14040.51318070868</v>
       </c>
       <c r="AH3">
-        <v>121073.30723357247</v>
+        <v>120968.77969974287</v>
       </c>
       <c r="AI3">
-        <v>121073.30723357247</v>
+        <v>120968.77969974287</v>
       </c>
       <c r="AJ3">
-        <v>13.432149037405283</v>
+        <v>13.42954322104451</v>
       </c>
       <c r="AK3">
-        <v>23.795012224292822</v>
+        <v>23.789882803726211</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1297,133 +1297,133 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-3.8880443980582142</v>
+        <v>-3.8850621396719633</v>
       </c>
       <c r="AO3">
-        <v>-5.4011654646761258</v>
+        <v>-5.39979776522121</v>
       </c>
       <c r="AP3">
-        <v>-9.6237776551548837</v>
+        <v>-9.61115916241059</v>
       </c>
       <c r="AQ3">
-        <v>-8.6039711768610232</v>
+        <v>-8.6005348400979145</v>
       </c>
       <c r="AR3">
-        <v>637.5351834070824</v>
+        <v>637.21364616718654</v>
       </c>
       <c r="AS3">
-        <v>3148.4546585183684</v>
+        <v>3146.4175424759178</v>
       </c>
       <c r="AT3">
-        <v>3.0575498867013131</v>
+        <v>3.0566275578015261</v>
       </c>
       <c r="AU3">
-        <v>96.0754423970784</v>
+        <v>96.202395367436679</v>
       </c>
       <c r="AV3">
-        <v>11.022234801318177</v>
+        <v>11.043603156089844</v>
       </c>
       <c r="AW3">
-        <v>-26.961101483801549</v>
+        <v>-26.989546669562756</v>
       </c>
       <c r="AX3">
-        <v>-4.6393873407322923</v>
+        <v>-4.649355413797946</v>
       </c>
       <c r="AY3">
         <v>0</v>
       </c>
       <c r="AZ3">
-        <v>2.2042907725058059</v>
+        <v>2.204950693708438</v>
       </c>
       <c r="BA3">
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>0.047984931598993891</v>
+        <v>0.048011446976628194</v>
       </c>
       <c r="BC3">
-        <v>0.12572742141088181</v>
+        <v>0.12603772467188645</v>
       </c>
       <c r="BD3">
-        <v>-0.018995285790098307</v>
+        <v>-0.016999901283362009</v>
       </c>
       <c r="BE3">
         <v>0</v>
       </c>
       <c r="BF3">
-        <v>-0.029794882360193339</v>
+        <v>-0.026678495329809246</v>
       </c>
       <c r="BG3">
         <v>0</v>
       </c>
       <c r="BH3">
-        <v>-21.909944070075959</v>
+        <v>-22.004593593723175</v>
       </c>
       <c r="BI3">
-        <v>-27.306868122348419</v>
+        <v>-27.327894103204748</v>
       </c>
       <c r="BJ3">
-        <v>-5.1268198540421785</v>
+        <v>-5.1368205950376229</v>
       </c>
       <c r="BK3">
         <v>0</v>
       </c>
       <c r="BL3">
-        <v>0.31389630660494294</v>
+        <v>0.30230365511339596</v>
       </c>
       <c r="BM3">
         <v>0</v>
       </c>
       <c r="BN3">
-        <v>-0.37062518213084106</v>
+        <v>-0.3558977161420307</v>
       </c>
       <c r="BO3">
         <v>90</v>
       </c>
       <c r="BP3">
-        <v>-0.21907475302938112</v>
+        <v>-0.21830993794687539</v>
       </c>
       <c r="BQ3">
-        <v>5.3255748598959132</v>
+        <v>5.3233120211075606</v>
       </c>
       <c r="BR3">
-        <v>21.035066563310455</v>
+        <v>21.030015700381803</v>
       </c>
       <c r="BS3">
-        <v>-11.796548274163133</v>
+        <v>-11.789247555411787</v>
       </c>
       <c r="BT3">
-        <v>-7.06719094606822</v>
+        <v>-7.0643538643435937</v>
       </c>
       <c r="BU3">
-        <v>29.146500022784359</v>
+        <v>29.140030953308443</v>
       </c>
       <c r="BV3">
-        <v>-11.367121201282988</v>
+        <v>-11.362665691812458</v>
       </c>
       <c r="BW3">
-        <v>-38.703194064739613</v>
+        <v>-38.69508069623128</v>
       </c>
       <c r="BX3">
-        <v>-18.386144278631175</v>
+        <v>-18.446906144584137</v>
       </c>
       <c r="BY3">
         <v>0</v>
       </c>
       <c r="BZ3">
-        <v>40.267634384237347</v>
+        <v>40.410969006708704</v>
       </c>
       <c r="CA3">
         <v>0</v>
       </c>
       <c r="CB3">
-        <v>161.45017746866176</v>
+        <v>161.59351154414028</v>
       </c>
       <c r="CC3">
         <v>0</v>
       </c>
       <c r="CD3">
-        <v>1.2697415587529561</v>
+        <v>1.2686152930342316</v>
       </c>
       <c r="CE3">
         <v>1E+307</v>
@@ -2278,112 +2278,112 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>333.98357778847736</v>
+        <v>333.98357778847742</v>
       </c>
       <c r="C3">
-        <v>74.307983959854383</v>
+        <v>74.279155486085955</v>
       </c>
       <c r="D3">
-        <v>7.1826470196418839</v>
+        <v>7.1798604449003944</v>
       </c>
       <c r="E3">
         <v>96.660501831436832</v>
       </c>
       <c r="F3">
-        <v>103.99962177835239</v>
+        <v>103.95927415742942</v>
       </c>
       <c r="G3">
-        <v>474.06987630185256</v>
+        <v>473.86551064294986</v>
       </c>
       <c r="H3">
-        <v>8.3056288422955333</v>
+        <v>8.3024065963072751</v>
       </c>
       <c r="I3">
-        <v>79.862106229547422</v>
+        <v>79.862106229547436</v>
       </c>
       <c r="J3">
         <v>2705.1966216148621</v>
       </c>
       <c r="K3">
-        <v>1016.5170773683535</v>
+        <v>1014.0352146956549</v>
       </c>
       <c r="L3">
-        <v>840.660769468848</v>
+        <v>838.13784644841292</v>
       </c>
       <c r="M3">
         <v>5.3007432949812827</v>
       </c>
       <c r="N3">
-        <v>2.4524488614793163</v>
+        <v>2.4476277699213393</v>
       </c>
       <c r="O3">
-        <v>2.1090802151273267</v>
+        <v>2.1028358569718293</v>
       </c>
       <c r="P3">
         <v>5.3007432949812827</v>
       </c>
       <c r="Q3">
-        <v>2.4524488614793163</v>
+        <v>2.4476277699213393</v>
       </c>
       <c r="R3">
-        <v>2.1090802151273267</v>
+        <v>2.1028358569718293</v>
       </c>
       <c r="S3">
         <v>100</v>
       </c>
       <c r="T3">
-        <v>222.84382391576858</v>
+        <v>223.28182482446738</v>
       </c>
       <c r="U3">
-        <v>173.51537049253355</v>
+        <v>174.03012998639335</v>
       </c>
       <c r="V3">
         <v>6.1230317691118863E-15</v>
       </c>
       <c r="W3">
-        <v>863.25008660391779</v>
+        <v>864.16869317101214</v>
       </c>
       <c r="X3">
-        <v>-1.7310505108592154</v>
+        <v>-2.654004051447219</v>
       </c>
       <c r="Y3">
-        <v>14.403836784160129</v>
+        <v>14.401042461863272</v>
       </c>
       <c r="Z3">
-        <v>28.629221472316949</v>
+        <v>28.623049955528398</v>
       </c>
       <c r="AA3">
-        <v>8.4977359036537372</v>
+        <v>8.4961855601191925</v>
       </c>
       <c r="AB3">
-        <v>8.9348379579812924</v>
+        <v>8.9312659082442742</v>
       </c>
       <c r="AC3">
-        <v>6.4284351206741626</v>
+        <v>6.4284909212768566</v>
       </c>
       <c r="AD3">
-        <v>3.702975538147343</v>
+        <v>3.7023287925477355</v>
       </c>
       <c r="AE3">
-        <v>602.43269263170532</v>
+        <v>601.97261197453577</v>
       </c>
       <c r="AF3">
-        <v>5992.0040733827327</v>
+        <v>5985.7978485632621</v>
       </c>
       <c r="AG3">
-        <v>6773.89293937973</v>
+        <v>6768.6392304381379</v>
       </c>
       <c r="AH3">
-        <v>121073.30723357247</v>
+        <v>120968.77969974287</v>
       </c>
       <c r="AI3">
-        <v>121073.30723357247</v>
+        <v>120968.77969974287</v>
       </c>
       <c r="AJ3">
-        <v>11.971665827071861</v>
+        <v>11.96934334221922</v>
       </c>
       <c r="AK3">
-        <v>23.795012224292822</v>
+        <v>23.789882803726211</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2392,136 +2392,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-3.3683030837796335</v>
+        <v>-3.3676685905782726</v>
       </c>
       <c r="AO3">
-        <v>-5.4011654646761258</v>
+        <v>-5.39979776522121</v>
       </c>
       <c r="AP3">
-        <v>-8.1719951901937691</v>
+        <v>-8.17050414261495</v>
       </c>
       <c r="AQ3">
-        <v>-8.6039711768610232</v>
+        <v>-8.6005348400979145</v>
       </c>
       <c r="AR3">
-        <v>342.33107579067223</v>
+        <v>342.13166013274713</v>
       </c>
       <c r="AS3">
-        <v>3148.4546585183684</v>
+        <v>3146.4175424759178</v>
       </c>
       <c r="AT3">
-        <v>4.8250356926644526</v>
+        <v>4.8261601890014445</v>
       </c>
       <c r="AU3">
-        <v>96.126348114952677</v>
+        <v>96.2595455480762</v>
       </c>
       <c r="AV3">
-        <v>11.340043330385781</v>
+        <v>11.363865294326253</v>
       </c>
       <c r="AW3">
-        <v>-27.092348373739096</v>
+        <v>-27.121178036800043</v>
       </c>
       <c r="AX3">
-        <v>-1.1690200611656514</v>
+        <v>-1.171588245901823</v>
       </c>
       <c r="AY3">
-        <v>-2.7416285743153552</v>
+        <v>-2.744529424630449</v>
       </c>
       <c r="AZ3">
-        <v>0.61209981583750039</v>
+        <v>0.61231969893369242</v>
       </c>
       <c r="BA3">
-        <v>-9.7561782128209238</v>
+        <v>-9.7692803874495251</v>
       </c>
       <c r="BB3">
-        <v>0.16464106884946378</v>
+        <v>0.16474611918038726</v>
       </c>
       <c r="BC3">
-        <v>0.39599230788951378</v>
+        <v>0.39698539673824429</v>
       </c>
       <c r="BD3">
-        <v>-0.10111861321305869</v>
+        <v>-0.10034914866264963</v>
       </c>
       <c r="BE3">
-        <v>13.863439164294631</v>
+        <v>13.876354726478379</v>
       </c>
       <c r="BF3">
-        <v>-0.29538251232234158</v>
+        <v>-0.29330564912850843</v>
       </c>
       <c r="BG3">
-        <v>4.4032519657814051</v>
+        <v>4.4102076533552079</v>
       </c>
       <c r="BH3">
-        <v>-24.012569397508344</v>
+        <v>-24.023887171772174</v>
       </c>
       <c r="BI3">
-        <v>-27.306868122348419</v>
+        <v>-27.327894103204748</v>
       </c>
       <c r="BJ3">
-        <v>-1.3169347207864708</v>
+        <v>-1.3193864070909553</v>
       </c>
       <c r="BK3">
-        <v>2.0395983369146653</v>
+        <v>2.0466789067022004</v>
       </c>
       <c r="BL3">
-        <v>0.08340880734733902</v>
+        <v>0.082303951431130618</v>
       </c>
       <c r="BM3">
-        <v>-9.9267103908535113</v>
+        <v>-9.9389328654603837</v>
       </c>
       <c r="BN3">
-        <v>-0.32272744998938779</v>
+        <v>-0.31786464348791016</v>
       </c>
       <c r="BO3">
-        <v>-13.542907042516537</v>
+        <v>-13.511535753031087</v>
       </c>
       <c r="BP3">
-        <v>0.39490466445033384</v>
+        <v>0.39517679866179711</v>
       </c>
       <c r="BQ3">
-        <v>4.0474770170785517</v>
+        <v>4.04667055761045</v>
       </c>
       <c r="BR3">
-        <v>18.836074781710256</v>
+        <v>18.831547464192532</v>
       </c>
       <c r="BS3">
-        <v>-10.075844810778936</v>
+        <v>-10.075584069505144</v>
       </c>
       <c r="BT3">
-        <v>8.1621346184775874</v>
+        <v>8.164836453679321</v>
       </c>
       <c r="BU3">
-        <v>8.1964148658638827</v>
+        <v>8.1898766199656823</v>
       </c>
       <c r="BV3">
-        <v>-25.854470566326686</v>
+        <v>-25.856919514956559</v>
       </c>
       <c r="BW3">
-        <v>-14.483863889369358</v>
+        <v>-14.465369694559504</v>
       </c>
       <c r="BX3">
-        <v>-8.8527605682915986</v>
+        <v>-8.8741823390086125</v>
       </c>
       <c r="BY3">
-        <v>3.4591577399853186</v>
+        <v>3.4711352813565308</v>
       </c>
       <c r="BZ3">
-        <v>21.794144884701055</v>
+        <v>21.854393781125367</v>
       </c>
       <c r="CA3">
-        <v>-7.0499030634387578</v>
+        <v>-7.0704692175146953</v>
       </c>
       <c r="CB3">
-        <v>101.65668025974354</v>
+        <v>101.71692289203901</v>
       </c>
       <c r="CC3">
-        <v>5.59949999055792</v>
+        <v>5.61237130696027</v>
       </c>
       <c r="CD3">
-        <v>2.0165915262647114</v>
+        <v>2.0153971843759395</v>
       </c>
       <c r="CE3">
-        <v>36.610411705630582</v>
+        <v>36.526450013342135</v>
       </c>
     </row>
   </sheetData>
@@ -3373,10 +3373,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>333.98357778847736</v>
+        <v>333.98357778847742</v>
       </c>
       <c r="C3">
-        <v>74.307983959854383</v>
+        <v>74.279155486085955</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -3385,10 +3385,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>74.3079839598544</v>
+        <v>74.279155486085955</v>
       </c>
       <c r="G3">
-        <v>474.06987630185256</v>
+        <v>473.86551064294986</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -3400,85 +3400,85 @@
         <v>2705.1966216148621</v>
       </c>
       <c r="K3">
-        <v>1086.906967686801</v>
+        <v>1084.4325919837384</v>
       </c>
       <c r="L3">
-        <v>833.58987343100978</v>
+        <v>831.32734205310555</v>
       </c>
       <c r="M3">
         <v>5.3007432949812827</v>
       </c>
       <c r="N3">
-        <v>2.581523496348725</v>
+        <v>2.5767752348378576</v>
       </c>
       <c r="O3">
-        <v>2.0955913344340948</v>
+        <v>2.0898436292929712</v>
       </c>
       <c r="P3">
         <v>5.3007432949812827</v>
       </c>
       <c r="Q3">
-        <v>2.581523496348725</v>
+        <v>2.5767752348378576</v>
       </c>
       <c r="R3">
-        <v>2.0955913344340948</v>
+        <v>2.0898436292929712</v>
       </c>
       <c r="S3">
         <v>100</v>
       </c>
       <c r="T3">
-        <v>214.85916086090137</v>
+        <v>215.28334026123346</v>
       </c>
       <c r="U3">
-        <v>191.85198874608352</v>
+        <v>191.70438198080782</v>
       </c>
       <c r="V3">
         <v>6.1230317691118863E-15</v>
       </c>
       <c r="W3">
-        <v>832.31918193490344</v>
+        <v>833.21212087592164</v>
       </c>
       <c r="X3">
-        <v>-5.4877396598104644</v>
+        <v>-6.3634684949142386</v>
       </c>
       <c r="Y3">
-        <v>13.235958125984981</v>
+        <v>13.233390370360835</v>
       </c>
       <c r="Z3">
-        <v>28.629221472316949</v>
+        <v>28.623049955528398</v>
       </c>
       <c r="AA3">
-        <v>7.45667416736968</v>
+        <v>7.4613236518486659</v>
       </c>
       <c r="AB3">
-        <v>8.9348379579812924</v>
+        <v>8.9312659082442742</v>
       </c>
       <c r="AC3">
-        <v>6.17221345957636</v>
+        <v>6.1761414402417945</v>
       </c>
       <c r="AD3">
-        <v>3.702975538147343</v>
+        <v>3.7023287925477355</v>
       </c>
       <c r="AE3">
-        <v>326.04272338297534</v>
+        <v>326.09502379808629</v>
       </c>
       <c r="AF3">
-        <v>5992.0040733827327</v>
+        <v>5985.7978485632621</v>
       </c>
       <c r="AG3">
-        <v>4083.6855405727129</v>
+        <v>4080.5696662583346</v>
       </c>
       <c r="AH3">
-        <v>121073.30723357247</v>
+        <v>120968.77969974287</v>
       </c>
       <c r="AI3">
-        <v>121073.30723357247</v>
+        <v>120968.77969974287</v>
       </c>
       <c r="AJ3">
-        <v>11.00099021947144</v>
+        <v>10.998856044201443</v>
       </c>
       <c r="AK3">
-        <v>23.795012224292822</v>
+        <v>23.789882803726211</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-3.0237331209569396</v>
+        <v>-3.0242940305866228</v>
       </c>
       <c r="AO3">
-        <v>-5.4011654646761258</v>
+        <v>-5.39979776522121</v>
       </c>
       <c r="AP3">
-        <v>-7.1731519706954376</v>
+        <v>-7.1776138032760617</v>
       </c>
       <c r="AQ3">
-        <v>-8.6039711768610232</v>
+        <v>-8.6005348400979145</v>
       </c>
       <c r="AR3">
-        <v>224.25294420828763</v>
+        <v>224.114271244821</v>
       </c>
       <c r="AS3">
-        <v>3148.4546585183684</v>
+        <v>3146.4175424759178</v>
       </c>
       <c r="AT3">
-        <v>6.6399411480402293</v>
+        <v>6.6426118540400809</v>
       </c>
       <c r="AU3">
-        <v>96.082431373561249</v>
+        <v>96.221213590738088</v>
       </c>
       <c r="AV3">
-        <v>11.59654461180998</v>
+        <v>11.6225511354643</v>
       </c>
       <c r="AW3">
-        <v>-27.218794316590206</v>
+        <v>-27.247995519566622</v>
       </c>
       <c r="AX3">
         <v>0</v>
       </c>
       <c r="AY3">
-        <v>-10.983900930167103</v>
+        <v>-10.9955557794113</v>
       </c>
       <c r="AZ3">
         <v>0</v>
       </c>
       <c r="BA3">
-        <v>-39.027737390197316</v>
+        <v>-39.0809708075248</v>
       </c>
       <c r="BB3">
-        <v>0.32763452542894289</v>
+        <v>0.32786341938513708</v>
       </c>
       <c r="BC3">
-        <v>0.72568680592982315</v>
+        <v>0.72753491488924071</v>
       </c>
       <c r="BD3">
         <v>0</v>
       </c>
       <c r="BE3">
-        <v>27.7368811003784</v>
+        <v>27.763464327050446</v>
       </c>
       <c r="BF3">
         <v>0</v>
       </c>
       <c r="BG3">
-        <v>8.8096809732782049</v>
+        <v>8.823833439856605</v>
       </c>
       <c r="BH3">
-        <v>-25.398377579126812</v>
+        <v>-25.35404661630368</v>
       </c>
       <c r="BI3">
-        <v>-27.306868122348419</v>
+        <v>-27.327894103204748</v>
       </c>
       <c r="BJ3">
         <v>0</v>
       </c>
       <c r="BK3">
-        <v>8.1443317676388851</v>
+        <v>8.1729908686144981</v>
       </c>
       <c r="BL3">
         <v>0</v>
       </c>
       <c r="BM3">
-        <v>-39.717505277906859</v>
+        <v>-39.767156629790556</v>
       </c>
       <c r="BN3">
         <v>90</v>
       </c>
       <c r="BO3">
-        <v>-13.568934615724238</v>
+        <v>-13.537137702777031</v>
       </c>
       <c r="BP3">
-        <v>-5.9903561621270631</v>
+        <v>-5.9942977893384013</v>
       </c>
       <c r="BQ3">
-        <v>13.960953054931904</v>
+        <v>13.959311062682426</v>
       </c>
       <c r="BR3">
-        <v>-8.9891297992708488</v>
+        <v>-8.9935380969155361</v>
       </c>
       <c r="BS3">
-        <v>-17.329411046702493</v>
+        <v>-17.324895772157912</v>
       </c>
       <c r="BT3">
-        <v>8.1584104168908667</v>
+        <v>8.1611760879937254</v>
       </c>
       <c r="BU3">
-        <v>8.20012180720941</v>
+        <v>8.19352416401823</v>
       </c>
       <c r="BV3">
-        <v>-25.847888359702658</v>
+        <v>-25.850453252353951</v>
       </c>
       <c r="BW3">
-        <v>-14.495607223403166</v>
+        <v>-14.47692211248941</v>
       </c>
       <c r="BX3">
         <v>0</v>
       </c>
       <c r="BY3">
-        <v>13.82193189694395</v>
+        <v>13.870310850924829</v>
       </c>
       <c r="BZ3">
         <v>0</v>
       </c>
       <c r="CA3">
-        <v>-28.181702072359254</v>
+        <v>-28.264799451333804</v>
       </c>
       <c r="CB3">
         <v>0</v>
       </c>
       <c r="CC3">
-        <v>16.390737634856357</v>
+        <v>16.439147169960329</v>
       </c>
       <c r="CD3">
         <v>1E+307</v>
       </c>
       <c r="CE3">
-        <v>12.507063718965846</v>
+        <v>12.470233271869583</v>
       </c>
     </row>
   </sheetData>
